--- a/verificables revisión sistemática/S5_listado_137_estudios.xlsx
+++ b/verificables revisión sistemática/S5_listado_137_estudios.xlsx
@@ -685,7 +685,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-14</t>
+          <t>Generado el 2026-09-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S5_listado_137_estudios.xlsx
+++ b/verificables revisión sistemática/S5_listado_137_estudios.xlsx
@@ -685,7 +685,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-15</t>
+          <t>Generado el 2026-09-16</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S5_listado_137_estudios.xlsx
+++ b/verificables revisión sistemática/S5_listado_137_estudios.xlsx
@@ -685,7 +685,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-16</t>
+          <t>Generado el 2026-09-22</t>
         </is>
       </c>
     </row>
